--- a/artfynd/A 30608-2023 artfynd.xlsx
+++ b/artfynd/A 30608-2023 artfynd.xlsx
@@ -2799,7 +2799,7 @@
         <v>136193898</v>
       </c>
       <c r="B21" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>136193899</v>
       </c>
       <c r="B22" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         <v>136193900</v>
       </c>
       <c r="B23" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3162,7 +3162,7 @@
         <v>136193901</v>
       </c>
       <c r="B24" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
         <v>136193902</v>
       </c>
       <c r="B25" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
         <v>136193903</v>
       </c>
       <c r="B26" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
         <v>136193904</v>
       </c>
       <c r="B27" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>136193905</v>
       </c>
       <c r="B28" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 30608-2023 artfynd.xlsx
+++ b/artfynd/A 30608-2023 artfynd.xlsx
@@ -2799,7 +2799,7 @@
         <v>136193898</v>
       </c>
       <c r="B21" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>136193899</v>
       </c>
       <c r="B22" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         <v>136193900</v>
       </c>
       <c r="B23" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3162,7 +3162,7 @@
         <v>136193901</v>
       </c>
       <c r="B24" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
         <v>136193902</v>
       </c>
       <c r="B25" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
         <v>136193903</v>
       </c>
       <c r="B26" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
         <v>136193904</v>
       </c>
       <c r="B27" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>136193905</v>
       </c>
       <c r="B28" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 30608-2023 artfynd.xlsx
+++ b/artfynd/A 30608-2023 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136193894</v>
       </c>
       <c r="B3" t="n">
-        <v>79231</v>
+        <v>79233</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>136193895</v>
       </c>
       <c r="B4" t="n">
-        <v>79231</v>
+        <v>79233</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>136193898</v>
       </c>
       <c r="B21" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>136193899</v>
       </c>
       <c r="B22" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         <v>136193900</v>
       </c>
       <c r="B23" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3162,7 +3162,7 @@
         <v>136193901</v>
       </c>
       <c r="B24" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
         <v>136193902</v>
       </c>
       <c r="B25" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
         <v>136193903</v>
       </c>
       <c r="B26" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
         <v>136193904</v>
       </c>
       <c r="B27" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>136193905</v>
       </c>
       <c r="B28" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 30608-2023 artfynd.xlsx
+++ b/artfynd/A 30608-2023 artfynd.xlsx
@@ -2799,7 +2799,7 @@
         <v>136193898</v>
       </c>
       <c r="B21" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>136193899</v>
       </c>
       <c r="B22" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         <v>136193900</v>
       </c>
       <c r="B23" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3162,7 +3162,7 @@
         <v>136193901</v>
       </c>
       <c r="B24" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
         <v>136193902</v>
       </c>
       <c r="B25" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
         <v>136193903</v>
       </c>
       <c r="B26" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
         <v>136193904</v>
       </c>
       <c r="B27" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>136193905</v>
       </c>
       <c r="B28" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
